--- a/AAII_Financials/Yearly/BBDO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BBDO_YR_FIN.xlsx
@@ -894,10 +894,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1571600</v>
+        <v>1571400</v>
       </c>
       <c r="E14" s="3">
-        <v>962700</v>
+        <v>962900</v>
       </c>
       <c r="F14" s="3">
         <v>1308900</v>
@@ -927,7 +927,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>840600</v>
+        <v>775600</v>
       </c>
       <c r="E15" s="3">
         <v>799300</v>
@@ -972,10 +972,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>11210600</v>
+        <v>11210900</v>
       </c>
       <c r="E17" s="3">
-        <v>9306900</v>
+        <v>9306600</v>
       </c>
       <c r="F17" s="3">
         <v>11106700</v>
@@ -1005,10 +1005,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4996100</v>
+        <v>4995800</v>
       </c>
       <c r="E18" s="3">
-        <v>3447600</v>
+        <v>3447900</v>
       </c>
       <c r="F18" s="3">
         <v>2979600</v>
@@ -1086,10 +1086,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6229300</v>
+        <v>6164000</v>
       </c>
       <c r="E21" s="3">
-        <v>4494500</v>
+        <v>4494700</v>
       </c>
       <c r="F21" s="3">
         <v>4756500</v>
@@ -1682,10 +1682,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>44516000</v>
+        <v>99453500</v>
       </c>
       <c r="E42" s="3">
-        <v>32974500</v>
+        <v>60127600</v>
       </c>
       <c r="F42" s="3">
         <v>42399000</v>
@@ -1715,10 +1715,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1480800</v>
+        <v>3609100</v>
       </c>
       <c r="E43" s="3">
-        <v>2836300</v>
+        <v>4367600</v>
       </c>
       <c r="F43" s="3">
         <v>4351700</v>
@@ -1781,10 +1781,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5378700</v>
+        <v>4322500</v>
       </c>
       <c r="E45" s="3">
-        <v>4071500</v>
+        <v>3515500</v>
       </c>
       <c r="F45" s="3">
         <v>4284100</v>
@@ -1814,10 +1814,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>83294700</v>
+        <v>133868400</v>
       </c>
       <c r="E46" s="3">
-        <v>64729600</v>
+        <v>92858100</v>
       </c>
       <c r="F46" s="3">
         <v>83043700</v>
@@ -1847,10 +1847,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>171509200</v>
+        <v>74769100</v>
       </c>
       <c r="E47" s="3">
-        <v>128117600</v>
+        <v>70221600</v>
       </c>
       <c r="F47" s="3">
         <v>158658500</v>
@@ -2012,10 +2012,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8862200</v>
+        <v>9954100</v>
       </c>
       <c r="E52" s="3">
-        <v>8183000</v>
+        <v>9128600</v>
       </c>
       <c r="F52" s="3">
         <v>6381000</v>
@@ -2174,7 +2174,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>83084200</v>
+        <v>122151200</v>
       </c>
       <c r="E58" s="3">
         <v>50425800</v>
@@ -2207,7 +2207,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>81588400</v>
+        <v>85902600</v>
       </c>
       <c r="E59" s="3">
         <v>7235100</v>
@@ -2240,7 +2240,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>299091300</v>
+        <v>342472500</v>
       </c>
       <c r="E60" s="3">
         <v>164384700</v>
@@ -2273,7 +2273,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>65183200</v>
+        <v>26116200</v>
       </c>
       <c r="E61" s="3">
         <v>63686200</v>
@@ -2306,7 +2306,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>25972900</v>
+        <v>21658700</v>
       </c>
       <c r="E62" s="3">
         <v>78947400</v>
@@ -2902,7 +2902,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>453800</v>
+        <v>444000</v>
       </c>
       <c r="E83" s="3">
         <v>424000</v>
